--- a/admin/ReportExcel/companyBankReport.xlsx
+++ b/admin/ReportExcel/companyBankReport.xlsx
@@ -15,18 +15,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24">
-  <si>
-    <t>Date: 04-08-2026</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
+  <si>
+    <t>Date: 08-08-2026</t>
   </si>
   <si>
     <t>SUB :PAYMENT SHEET</t>
   </si>
   <si>
-    <t>SITE :Baroda Office Staff</t>
-  </si>
-  <si>
-    <t>Month : July-2026 - Bank Of Baroda - Bank Payment</t>
+    <t>SITE :Vedanta Limited., Barmer</t>
+  </si>
+  <si>
+    <t>Month : January-2025 - Bank Of Baroda - Bank Payment</t>
   </si>
   <si>
     <t>Sr. No.</t>
@@ -47,34 +47,52 @@
     <t xml:space="preserve"> 1 </t>
   </si>
   <si>
-    <t>09850100006866</t>
-  </si>
-  <si>
-    <t>Jitendrabhai Raysingbhai Padhiyar</t>
-  </si>
-  <si>
-    <t>BARB0PADAML</t>
+    <t>02940100027424</t>
+  </si>
+  <si>
+    <t>Vahora Rajjakbhai Sattarbhai</t>
+  </si>
+  <si>
+    <t>BARB0ANANDX</t>
   </si>
   <si>
     <t xml:space="preserve"> 2 </t>
   </si>
   <si>
-    <t>02130100012524</t>
-  </si>
-  <si>
-    <t>Kiran Udesinh Gohil</t>
-  </si>
-  <si>
-    <t>BARB0RANOLI</t>
+    <t>03040100010870</t>
+  </si>
+  <si>
+    <t>Bharatsinh Ratansinh Sindha</t>
+  </si>
+  <si>
+    <t>BARB0DHUVAR</t>
   </si>
   <si>
     <t xml:space="preserve"> 3 </t>
   </si>
   <si>
-    <t>02130100009478</t>
-  </si>
-  <si>
-    <t>Chhatrasing Shankarbhai Vaghela</t>
+    <t>03040100019123</t>
+  </si>
+  <si>
+    <t>Bhikhabhai Himmatsinh Sindha</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4 </t>
+  </si>
+  <si>
+    <t>03040100010817</t>
+  </si>
+  <si>
+    <t>Devjibhai Gulabbhai Thakor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5 </t>
+  </si>
+  <si>
+    <t>03040100010363</t>
+  </si>
+  <si>
+    <t>Khodabhai Mangalbhai Raval</t>
   </si>
   <si>
     <t>Total Amt.</t>
@@ -494,7 +512,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="true" style="0"/>
@@ -550,7 +568,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="5">
-        <v>12690.0</v>
+        <v>9193.0</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>11</v>
@@ -567,7 +585,7 @@
         <v>14</v>
       </c>
       <c r="C8" s="5">
-        <v>13227.0</v>
+        <v>7827.0</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>15</v>
@@ -584,7 +602,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="5">
-        <v>12690.0</v>
+        <v>5571.0</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>19</v>
@@ -593,32 +611,66 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:5" customHeight="1" ht="30">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6" t="s">
+    <row r="10" spans="1:5" customHeight="1" ht="20">
+      <c r="A10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="7">
-        <v>38607.0</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-    </row>
-    <row r="12" spans="1:5" customHeight="1" ht="20">
-      <c r="E12" s="1" t="s">
+      <c r="B10" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="C10" s="5">
+        <v>7827.0</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" customHeight="1" ht="20">
+      <c r="A11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="5">
+        <v>5571.0</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" customHeight="1" ht="30">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="7">
+        <v>35989.0</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
     </row>
     <row r="14" spans="1:5" customHeight="1" ht="20">
       <c r="E14" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" customHeight="1" ht="20">
-      <c r="B15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="8"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" customHeight="1" ht="20">
+      <c r="E16" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" customHeight="1" ht="20">
+      <c r="B17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="8"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
